--- a/output/2026-09-16_04_Croazia_Zadarska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-16_04_Croazia_Zadarska_Depolverazione_Trattamento_aria.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Centro Kärcher ufficiale autorizzato (confermato su karcher.com dealer locator). Rivenditore/assistenza aspiratori industriali e professionali Kärcher. Lieve discordanza sull'ultima cifra del cellulare tra fonti: verificare telefonicamente.</t>
+          <t>Centro Kärcher ufficiale autorizzato (confermato su karcher.com dealer locator). Rivenditore/assistenza aspiratori industriali e professionali Kärcher. Lieve discordanza sull'ultima cifra del cellulare tra fonti: verificare telefonicamente. [DUPLICATO — vedi anche: 2026-09-16_03_Croazia_Zadarska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
